--- a/backend/uploads/templates/template-import-parent.xlsx
+++ b/backend/uploads/templates/template-import-parent.xlsx
@@ -4,6 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Orang Tua" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -398,12 +399,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D2"/>
-  <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -438,4 +433,56 @@
     <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="25.83203125" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>NIS</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Nama</v>
+      </c>
+      <c r="C1" t="str">
+        <v>No. WA</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Email</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Password</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1234567890</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Orang Tua Contoh</v>
+      </c>
+      <c r="C2" t="str">
+        <v>081234567890</v>
+      </c>
+      <c r="D2" t="str">
+        <v>parent@example.com</v>
+      </c>
+      <c r="E2" t="str">
+        <v>password123</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+  </ignoredErrors>
+</worksheet>
 </file>